--- a/data/trans_orig/P34B01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P34B01-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población camina durante más de 30 minutos</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población camina (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,37 +677,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,52</t>
+          <t>2,72; 3,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,36</t>
+          <t>3,72; 4,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,3</t>
+          <t>3,75; 4,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,17</t>
+          <t>2,46; 3,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,32</t>
+          <t>3,7; 4,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 3,93</t>
+          <t>3,54; 3,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,22</t>
+          <t>2,73; 3,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 4,06</t>
+          <t>3,71; 4,06</t>
         </is>
       </c>
     </row>
@@ -787,37 +787,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,3</t>
+          <t>2,77; 3,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,52</t>
+          <t>3,03; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,56</t>
+          <t>3,01; 3,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,02</t>
+          <t>2,51; 3,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,39</t>
+          <t>2,91; 3,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,02</t>
+          <t>2,6; 3,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,06</t>
+          <t>2,69; 3,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,22</t>
+          <t>2,88; 3,23</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,86</t>
+          <t>2,23; 2,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,27</t>
+          <t>3,6; 4,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,37</t>
+          <t>2,64; 3,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,63</t>
+          <t>3,02; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,53</t>
+          <t>3,9; 4,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,45</t>
+          <t>2,92; 3,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,15</t>
+          <t>2,72; 3,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,33</t>
+          <t>3,85; 4,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,35</t>
+          <t>2,91; 3,34</t>
         </is>
       </c>
     </row>
@@ -1007,37 +1007,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,63</t>
+          <t>1,97; 2,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 4,97</t>
+          <t>4,43; 5,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,39</t>
+          <t>2,49; 3,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,07</t>
+          <t>2,45; 3,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 4,39</t>
+          <t>3,74; 4,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,18</t>
+          <t>2,18; 3,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,76</t>
+          <t>2,3; 2,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,15</t>
+          <t>2,41; 3,15</t>
         </is>
       </c>
     </row>
@@ -1117,37 +1117,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,98</t>
+          <t>2,11; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 3,54</t>
+          <t>2,77; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 6,29</t>
+          <t>5,81; 6,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,24</t>
+          <t>2,37; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,05</t>
+          <t>2,23; 3,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 5,92</t>
+          <t>5,5; 5,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,98</t>
+          <t>2,39; 2,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 6,03</t>
+          <t>5,74; 6,04</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 2,92</t>
+          <t>2,25; 2,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,5</t>
+          <t>1,73; 2,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,65</t>
+          <t>2,03; 2,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,53</t>
+          <t>2,89; 3,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,84</t>
+          <t>2,13; 2,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,67</t>
+          <t>2,12; 2,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,15</t>
+          <t>2,66; 3,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,55</t>
+          <t>2,05; 2,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,56</t>
+          <t>2,15; 2,56</t>
         </is>
       </c>
     </row>
@@ -1337,27 +1337,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,01</t>
+          <t>2,54; 2,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,75</t>
+          <t>3,25; 3,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,99; 4,55</t>
+          <t>3,98; 4,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,34</t>
+          <t>2,93; 3,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,61</t>
+          <t>3,17; 3,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,13</t>
+          <t>2,82; 3,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,62</t>
+          <t>3,29; 3,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,04</t>
+          <t>3,49; 4,04</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1447,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,57</t>
+          <t>2,15; 2,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,61</t>
+          <t>2,21; 2,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,53</t>
+          <t>2,15; 4,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 2,7</t>
+          <t>2,28; 2,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 2,57</t>
+          <t>2,27; 2,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,4</t>
+          <t>2,13; 2,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,24</t>
+          <t>2,76; 4,26</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 2,75</t>
+          <t>2,53; 2,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,21; 3,4</t>
+          <t>3,21; 3,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,24</t>
+          <t>3,05; 3,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 3,54</t>
+          <t>3,3; 3,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,3</t>
+          <t>3,15; 3,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,64</t>
+          <t>3,18; 3,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P34B01-Provincia-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 3,52</t>
+          <t>2,68; 3,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,38</t>
+          <t>3,71; 4,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 4,29</t>
+          <t>3,85; 4,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,24</t>
+          <t>2,5; 3,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 4,34</t>
+          <t>3,7; 4,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 3,96</t>
+          <t>3,57; 3,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,25</t>
+          <t>2,71; 3,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 4,26</t>
+          <t>3,78; 4,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,06</t>
+          <t>3,77; 4,09</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,31</t>
+          <t>2,75; 3,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,53</t>
+          <t>3,0; 3,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,59</t>
+          <t>3,03; 3,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,01</t>
+          <t>2,47; 3,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 3,39</t>
+          <t>2,9; 3,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,0</t>
+          <t>2,58; 2,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,07</t>
+          <t>2,72; 3,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,37</t>
+          <t>3,04; 3,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,23</t>
+          <t>2,89; 3,23</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,18</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,85</t>
+          <t>2,23; 2,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 4,27</t>
+          <t>3,64; 4,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,32</t>
+          <t>2,69; 3,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,63</t>
+          <t>3,02; 3,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,52</t>
+          <t>3,88; 4,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,47</t>
+          <t>2,91; 3,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 3,16</t>
+          <t>2,75; 3,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,29</t>
+          <t>3,84; 4,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 3,34</t>
+          <t>2,89; 3,33</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>3,09</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,61</t>
+          <t>1,99; 2,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,02</t>
+          <t>4,42; 4,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,37</t>
+          <t>2,59; 3,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,06</t>
+          <t>2,47; 3,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 4,36</t>
+          <t>3,77; 4,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,16</t>
+          <t>2,9; 3,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 2,75</t>
+          <t>2,31; 2,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 4,6</t>
+          <t>4,18; 4,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,15</t>
+          <t>2,85; 3,35</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>5,95</t>
         </is>
       </c>
     </row>
@@ -1122,42 +1122,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,52</t>
+          <t>2,78; 3,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 6,28</t>
+          <t>5,89; 6,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,21</t>
+          <t>2,4; 3,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,03</t>
+          <t>2,26; 3,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 5,88</t>
+          <t>5,61; 5,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 2,97</t>
+          <t>2,37; 2,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,17</t>
+          <t>2,6; 3,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 6,04</t>
+          <t>5,8; 6,06</t>
         </is>
       </c>
     </row>
@@ -1184,37 +1184,37 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3,22</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,48</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,38</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>2,33</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,38</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,9</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 2,91</t>
+          <t>2,24; 2,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,47</t>
+          <t>1,73; 2,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,65</t>
+          <t>2,03; 2,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,53</t>
+          <t>2,88; 3,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,84</t>
+          <t>2,16; 2,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,66</t>
+          <t>2,12; 2,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,12</t>
+          <t>2,71; 3,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 2,55</t>
+          <t>2,05; 2,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,56</t>
+          <t>2,14; 2,56</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>4,01</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 2,98</t>
+          <t>2,54; 3,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 3,75</t>
+          <t>3,26; 3,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 4,53</t>
+          <t>4,06; 4,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 3,36</t>
+          <t>2,93; 3,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,63</t>
+          <t>3,2; 3,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 3,76</t>
+          <t>3,51; 3,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,12</t>
+          <t>2,79; 3,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 3,61</t>
+          <t>3,28; 3,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,04</t>
+          <t>3,85; 4,17</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>4,25</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,56</t>
+          <t>2,16; 2,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,62</t>
+          <t>2,23; 2,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,53</t>
+          <t>4,32; 4,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 2,69</t>
+          <t>2,28; 2,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,31</t>
+          <t>1,93; 2,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,76; 4,12</t>
+          <t>3,79; 4,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 2,57</t>
+          <t>2,28; 2,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,39</t>
+          <t>2,12; 2,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,26</t>
+          <t>4,13; 4,39</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,72</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 2,74</t>
+          <t>2,54; 2,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,21; 3,41</t>
+          <t>3,2; 3,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,86</t>
+          <t>3,79; 4,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 2,97</t>
+          <t>2,77; 2,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,53</t>
+          <t>3,49; 3,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,29</t>
+          <t>3,16; 3,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,65</t>
+          <t>3,65; 3,79</t>
         </is>
       </c>
     </row>
